--- a/public/downloads/LiuCatalytic2022.xlsx
+++ b/public/downloads/LiuCatalytic2022.xlsx
@@ -1572,16 +1572,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2052544122868269</v>
+        <v>-0.1888449952704718</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3720516138509696</v>
+        <v>0.3720554171311405</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2927149178861876</v>
+        <v>0.291693370307847</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -2153,16 +2153,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.382964751526502</v>
+        <v>-1.061172384139468</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>1.396892794168885</v>
+        <v>1.36377529807051</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9694220965372377</v>
+        <v>0.9318889342924118</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -2726,16 +2726,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1566975592050208</v>
+        <v>-0.2444361386122864</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3269290212830954</v>
+        <v>0.3217679283767856</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3269290212830954</v>
+        <v>0.3217679283767856</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -3307,16 +3307,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1624374521649443</v>
+        <v>-0.07635629425209345</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8733028227040808</v>
+        <v>0.8234516829963221</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4234076138597302</v>
+        <v>0.3582176619341996</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3888,16 +3888,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5413107781329849</v>
+        <v>-0.6251596567987576</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6291884488880602</v>
+        <v>0.6180552329377801</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5364107044336097</v>
+        <v>0.5298222174030478</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -4469,22 +4469,22 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.221550374237192</v>
+        <v>-0.891594721899537</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8492489100448969</v>
+        <v>0.7980757990248603</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7252897671925876</v>
+        <v>0.5307231210629504</v>
       </c>
       <c r="R3" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -5050,16 +5050,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2030718841458816</v>
+        <v>0.219205041141322</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1190086944906573</v>
+        <v>0.1180596852556314</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1190086944906573</v>
+        <v>0.1180596852556314</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -5631,16 +5631,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.389709660462094</v>
+        <v>-1.103153283982351</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8406640411377534</v>
+        <v>0.819138132013346</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6656024533481478</v>
+        <v>0.624821401373481</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -6200,16 +6200,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3795880839590612</v>
+        <v>0.3683545128737933</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.238737694237507</v>
+        <v>0.2371536290921082</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.238737694237507</v>
+        <v>0.2371536290921082</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -6781,13 +6781,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5003813414492519</v>
+        <v>-0.5038299203851011</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4729078165178491</v>
+        <v>0.4727049589333874</v>
       </c>
       <c r="Q3" s="4">
         <v>0.4386991050383138</v>
@@ -7308,13 +7308,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>96.875</v>
+        <v>93.75</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>3.125</v>
+        <v>6.25</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -7323,16 +7323,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>3.125</v>
+        <v>6.25</v>
       </c>
       <c r="H3" s="4">
-        <v>0.5572853593052851</v>
+        <v>0.5403673114162135</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4550888871480147</v>
+        <v>0.3697575772590426</v>
       </c>
       <c r="J3" s="4">
-        <v>0.5512764867496177</v>
+        <v>0.516033119915507</v>
       </c>
       <c r="K3" s="4">
         <v>85.67814625850342</v>
@@ -7376,13 +7376,13 @@
         <v>15.625</v>
       </c>
       <c r="H4" s="4">
-        <v>3.074703713244333</v>
+        <v>3.095291767852489</v>
       </c>
       <c r="I4" s="4">
-        <v>0.7359292904874893</v>
+        <v>0.7184222591105396</v>
       </c>
       <c r="J4" s="4">
-        <v>1.476253887711636</v>
+        <v>1.492020164976042</v>
       </c>
       <c r="K4" s="4">
         <v>70.26785714285744</v>
@@ -7426,13 +7426,13 @@
         <v>6.25</v>
       </c>
       <c r="H5" s="4">
-        <v>0.6434505095499964</v>
+        <v>0.6444920137538528</v>
       </c>
       <c r="I5" s="4">
         <v>0.453240579698294</v>
       </c>
       <c r="J5" s="4">
-        <v>0.5538964808916557</v>
+        <v>0.5507719682800865</v>
       </c>
       <c r="K5" s="4">
         <v>80.01913265306122</v>
@@ -7476,13 +7476,13 @@
         <v>6.25</v>
       </c>
       <c r="H6" s="4">
-        <v>0.7004779419788646</v>
+        <v>0.6659879603481293</v>
       </c>
       <c r="I6" s="4">
-        <v>0.5151156804842972</v>
+        <v>0.455085829521575</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7161370292579153</v>
+        <v>0.7005975716748623</v>
       </c>
       <c r="K6" s="4">
         <v>89.73745748299321</v>
@@ -7526,13 +7526,13 @@
         <v>6.25</v>
       </c>
       <c r="H7" s="4">
-        <v>0.5236099497145795</v>
+        <v>0.5236844402777621</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3482745615157289</v>
+        <v>0.3478127765333248</v>
       </c>
       <c r="J7" s="4">
-        <v>0.510314384632054</v>
+        <v>0.5087160274053595</v>
       </c>
       <c r="K7" s="4">
         <v>87.29272959183673</v>
@@ -7576,13 +7576,13 @@
         <v>9.375</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7450552241303388</v>
+        <v>0.7450572446229295</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4704215912785199</v>
+        <v>0.4698378498051824</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7113013158224838</v>
+        <v>0.7113027192833937</v>
       </c>
       <c r="K8" s="4">
         <v>83.91900510204081</v>
@@ -7626,13 +7626,13 @@
         <v>15.625</v>
       </c>
       <c r="H9" s="4">
-        <v>2.2463788900976</v>
+        <v>2.228785220295338</v>
       </c>
       <c r="I9" s="4">
-        <v>0.994815450625382</v>
+        <v>0.9713572242223663</v>
       </c>
       <c r="J9" s="4">
-        <v>1.568179986298543</v>
+        <v>1.562804791838078</v>
       </c>
       <c r="K9" s="4">
         <v>77.06738945578225</v>
@@ -7676,13 +7676,13 @@
         <v>6.25</v>
       </c>
       <c r="H10" s="4">
-        <v>0.5486759177595182</v>
+        <v>0.5459340871530411</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3993493361801367</v>
+        <v>0.3964247168665612</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4803610641452496</v>
+        <v>0.4814523268015249</v>
       </c>
       <c r="K10" s="4">
         <v>89.9266581632653</v>
@@ -7726,13 +7726,13 @@
         <v>15.625</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8028737252781861</v>
+        <v>0.7763903073084393</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3808678587428616</v>
+        <v>0.3482728827800962</v>
       </c>
       <c r="J11" s="4">
-        <v>0.8240863627026551</v>
+        <v>0.8033268772433821</v>
       </c>
       <c r="K11" s="4">
         <v>82.89009353741497</v>
@@ -7776,13 +7776,13 @@
         <v>6.25</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8090683746048409</v>
+        <v>0.8031538536312546</v>
       </c>
       <c r="I12" s="4">
-        <v>0.5895952556435479</v>
+        <v>0.5859602283163412</v>
       </c>
       <c r="J12" s="4">
-        <v>0.80660916989655</v>
+        <v>0.8039888924382446</v>
       </c>
       <c r="K12" s="4">
         <v>89.44409013605443</v>
@@ -7808,13 +7808,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>84.375</v>
+        <v>81.25</v>
       </c>
       <c r="C13" s="3">
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>15.625</v>
+        <v>18.75</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -7823,16 +7823,16 @@
         <v>6.25</v>
       </c>
       <c r="G13" s="3">
-        <v>9.375</v>
+        <v>12.5</v>
       </c>
       <c r="H13" s="4">
-        <v>0.7875612478121634</v>
+        <v>0.7603755325827688</v>
       </c>
       <c r="I13" s="4">
-        <v>0.5650002205855865</v>
+        <v>0.4615519149589602</v>
       </c>
       <c r="J13" s="4">
-        <v>0.7666978754336279</v>
+        <v>0.7515417665991873</v>
       </c>
       <c r="K13" s="4">
         <v>76.18941326530613</v>
@@ -7876,13 +7876,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.21225012281485</v>
+        <v>0.2117459616587424</v>
       </c>
       <c r="I14" s="4">
-        <v>0.21225012281485</v>
+        <v>0.2117459616587424</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2181367184242325</v>
+        <v>0.217632557268125</v>
       </c>
       <c r="K14" s="4">
         <v>97.96556122448979</v>
@@ -7926,13 +7926,13 @@
         <v>34.375</v>
       </c>
       <c r="H15" s="4">
-        <v>1.906098089875196</v>
+        <v>1.894662450652855</v>
       </c>
       <c r="I15" s="4">
-        <v>0.738613222029054</v>
+        <v>0.7075419443340697</v>
       </c>
       <c r="J15" s="4">
-        <v>1.909312369064984</v>
+        <v>1.896496237840949</v>
       </c>
       <c r="K15" s="4">
         <v>87.70408163265306</v>
@@ -7976,13 +7976,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2245438167784456</v>
+        <v>0.2237022821699525</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2245438167784456</v>
+        <v>0.2237022821699525</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2328254542272595</v>
+        <v>0.2321744160634899</v>
       </c>
       <c r="K16" s="4">
         <v>95.13711734693878</v>
@@ -8026,13 +8026,13 @@
         <v>18.75</v>
       </c>
       <c r="H17" s="4">
-        <v>1.377025991882797</v>
+        <v>1.376918223791052</v>
       </c>
       <c r="I17" s="4">
         <v>0.69603150607708</v>
       </c>
       <c r="J17" s="4">
-        <v>1.374753361410536</v>
+        <v>1.374861129502281</v>
       </c>
       <c r="K17" s="4">
         <v>84.49936224489795</v>
@@ -8915,13 +8915,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -8930,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -9355,13 +9355,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="5">
         <v>0</v>
@@ -9729,22 +9729,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8391437532785697</v>
+        <v>-0.5338008170166404</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7460003714828991</v>
+        <v>0.7141546342799409</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5597893949392886</v>
+        <v>0.396106809014096</v>
       </c>
       <c r="R3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -10310,16 +10310,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6895140190234912</v>
+        <v>-0.5446969983594272</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>2.01745523332952</v>
+        <v>2.056209218474284</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8575448974870076</v>
+        <v>0.8342021889844078</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -10871,13 +10871,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3894277468913891</v>
+        <v>-0.3560996123679843</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3883560988153227</v>
+        <v>0.3903165773166994</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2914042102461956</v>
@@ -11452,16 +11452,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2971339135089615</v>
+        <v>0.0214592193587464</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7016855976147598</v>
+        <v>0.6367632792510228</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.437167182062317</v>
+        <v>0.3211094702010541</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -12033,16 +12033,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2331950573840835</v>
+        <v>-0.2174195948725242</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2332008508723657</v>
+        <v>0.2333410684030622</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1278356579653885</v>
+        <v>0.1269986726847812</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
